--- a/AAII_Financials/Quarterly/CSCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CSCO_QTR_FIN.xlsx
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E7" s="2">
         <v>46137</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44219</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44128</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44037</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43946</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43764</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43673</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43582</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43491</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43400</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43218</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43127</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17252000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15841000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15349000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14883000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14673000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14149000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13991000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13841000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13642000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12702000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12791000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14668000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15203000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14571000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13592000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13632000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13102000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12835000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12720000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12900000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13126000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12803000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11960000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11929000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12154000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11983000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12005000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13159000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13428000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12958000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12446000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13072000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12844000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12463000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11887000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12136000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12133000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>11940000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>11580000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>12352000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6189000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5761000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5377000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5138000</v>
       </c>
-      <c r="G9" s="3">
-        <v>5393000</v>
-      </c>
       <c r="H9" s="3">
+        <v>5412000</v>
+      </c>
+      <c r="I9" s="3">
         <v>4871000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4880000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4720000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4861000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4429000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4574000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5111000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5455000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5339000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5165000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5286000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5077000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4714000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4671000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4847000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4782000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4618000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4176000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4348000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4470000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4212000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4241000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4695000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4854000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4785000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4673000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4926000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4922000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4704000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4389000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4709000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4587000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4422000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4304000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4468000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11063000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10080000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9972000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9745000</v>
       </c>
-      <c r="G10" s="3">
-        <v>9280000</v>
-      </c>
       <c r="H10" s="3">
+        <v>9261000</v>
+      </c>
+      <c r="I10" s="3">
         <v>9278000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9111000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9121000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8781000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8273000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8217000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9557000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9748000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9232000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8427000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8346000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8025000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8121000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8049000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8053000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8344000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8185000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7784000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7581000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7684000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7771000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7764000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8464000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8574000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8173000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7773000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8146000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7922000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7759000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7498000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7427000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>7546000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7518000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7276000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7884000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1211,130 +1223,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2431000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2377000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2355000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2380000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2335000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2299000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2286000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2179000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1948000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1943000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1913000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1953000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1962000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1855000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1781000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1682000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1708000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1670000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1714000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1713000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1697000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1527000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1612000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1565000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1546000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1570000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1666000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1753000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1659000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1557000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1626000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1590000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1549000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1567000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1499000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1507000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1508000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1545000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1455,252 +1471,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-358000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-269000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-23000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-40000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-56000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="I14" s="3">
         <v>90000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>36000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>601000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>594000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>123000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>223000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>175000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>217000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>246000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>22000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>24000</v>
       </c>
       <c r="W14" s="3">
         <v>24000</v>
       </c>
       <c r="X14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="Y14" s="3">
         <v>57000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>230000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>595000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>128000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>127000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>41000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>181000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>29000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>168000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>65000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>93000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>103000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>161000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>152000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>70000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>133000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>411000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E15" s="3">
         <v>228000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>231000</v>
       </c>
       <c r="F15" s="3">
         <v>231000</v>
       </c>
       <c r="G15" s="3">
+        <v>231000</v>
+      </c>
+      <c r="H15" s="3">
         <v>254000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>244000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>265000</v>
       </c>
       <c r="J15" s="3">
         <v>265000</v>
       </c>
       <c r="K15" s="3">
+        <v>265000</v>
+      </c>
+      <c r="L15" s="3">
         <v>268000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>297000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>66000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>70000</v>
       </c>
       <c r="P15" s="3">
         <v>70000</v>
       </c>
       <c r="Q15" s="3">
-        <v>71000</v>
+        <v>70000</v>
       </c>
       <c r="R15" s="3">
         <v>71000</v>
       </c>
       <c r="S15" s="3">
+        <v>71000</v>
+      </c>
+      <c r="T15" s="3">
         <v>73000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>77000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>79000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>84000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>79000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>61000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>39000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>36000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>33000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>34000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>38000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>36000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>38000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>39000</v>
       </c>
       <c r="AG15" s="3">
         <v>39000</v>
       </c>
       <c r="AH15" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AI15" s="3">
         <v>34000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>67000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>60000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>61000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>58000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>59000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>64000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>12470000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11882000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11532000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11370000</v>
       </c>
-      <c r="G17" s="3">
-        <v>11551000</v>
-      </c>
       <c r="H17" s="3">
+        <v>11570000</v>
+      </c>
+      <c r="I17" s="3">
         <v>10913000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10868000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10809000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10994000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9920000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9683000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10238000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10729000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10538000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10300000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10092000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9668000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9225000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9233000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9462000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9551000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9338000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8737000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9359000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8907000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8569000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8625000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9580000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9738000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9445000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9235000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9267000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9498000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9329000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8814000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9380000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9099000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8771000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8687000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>9475000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4782000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3959000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3817000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3513000</v>
       </c>
-      <c r="G18" s="3">
-        <v>3122000</v>
-      </c>
       <c r="H18" s="3">
+        <v>3103000</v>
+      </c>
+      <c r="I18" s="3">
         <v>3236000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3123000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3032000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2648000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2782000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3108000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4430000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4474000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4033000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3292000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3540000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3434000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3610000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3487000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3438000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3575000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3465000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3223000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2570000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3247000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3414000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3380000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3579000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3690000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3513000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3211000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3805000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3346000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3134000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3073000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2756000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3034000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3169000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2893000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2877000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2028,618 +2060,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E20" s="3">
         <v>26000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>34000</v>
       </c>
       <c r="F20" s="3">
         <v>34000</v>
       </c>
       <c r="G20" s="3">
+        <v>34000</v>
+      </c>
+      <c r="H20" s="3">
         <v>38000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>46000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>32000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>94000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>28000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>29000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>230000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>35000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>75000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>281000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>204000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>308000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>258000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>237000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>145000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>223000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>178000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>162000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>313000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>286000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>220000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>315000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>358000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>325000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>470000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>355000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>406000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>441000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>367000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>242000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>289000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4954000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4161000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4014000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3710000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3338000</v>
-      </c>
       <c r="H21" s="3">
+        <v>3319000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3434000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3354000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3265000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2822000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3072000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3146000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4483000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4515000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4091000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3960000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3990000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3939000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4369000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4207000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4279000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4322000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4188000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3804000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3244000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3869000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4022000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4150000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4326000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4374000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4309000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4056000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4595000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4332000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4053000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4025000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3979000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3971000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3731000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3749000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E22" s="3">
         <v>377000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>370000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>350000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>368000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>403000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>404000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>418000</v>
       </c>
       <c r="K22" s="3">
         <v>418000</v>
       </c>
       <c r="L22" s="3">
+        <v>418000</v>
+      </c>
+      <c r="M22" s="3">
         <v>357000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>120000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>111000</v>
       </c>
       <c r="O22" s="3">
         <v>111000</v>
       </c>
       <c r="P22" s="3">
+        <v>111000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>109000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>107000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>93000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>90000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>88000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>89000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>98000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>111000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>113000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>112000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>119000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>132000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>159000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>179000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>206000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>213000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>226000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>221000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>224000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>236000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>247000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>235000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>221000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>220000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>219000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>197000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4933000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4039000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3646000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3391000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2999000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2947000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2887000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2267000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2396000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2235000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3161000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4442000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4471000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3957000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3415000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3475000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3416000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3801000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3603000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3657000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3735000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3591000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3255000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3306000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3444000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3534000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3686000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3704000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3615000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3343000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3909000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3592000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2962000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3180000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2963000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2953000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E24" s="3">
         <v>666000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>471000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>531000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>449000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>456000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>459000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-444000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>234000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>349000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>527000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>804000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>513000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>745000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>642000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>805000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>601000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>757000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>630000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>677000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>726000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>728000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>710000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>507000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>670000</v>
       </c>
       <c r="AB24" s="3">
         <v>670000</v>
       </c>
       <c r="AC24" s="3">
+        <v>670000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>656000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>760000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>684000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>571000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>463000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>360000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>562000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>910000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>568000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>756000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>676000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>615000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3859000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3373000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3175000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2860000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2550000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2491000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2428000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2711000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2162000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1886000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2634000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3638000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3958000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2773000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2670000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2815000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3044000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2973000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2980000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3009000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2863000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2878000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3020000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3044000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2880000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3549000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3103000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2322000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2424000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2515000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2348000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3859000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3373000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3175000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2860000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2550000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2491000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2428000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2711000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2162000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1886000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2634000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3638000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3958000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2773000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2670000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2815000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3044000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2973000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2980000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3009000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2863000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2878000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3020000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3044000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2880000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3549000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3103000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2322000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2424000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2515000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2348000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3191,8 +3251,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -3212,29 +3272,29 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-814000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-58000</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-11100000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3248,8 +3308,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,252 +3558,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-26000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-34000</v>
       </c>
       <c r="F32" s="3">
         <v>-34000</v>
       </c>
       <c r="G32" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-38000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-46000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-32000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-94000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-28000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-29000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-230000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-35000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-75000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-281000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-204000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-308000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-258000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-237000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-145000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-223000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-178000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-313000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-286000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-315000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-325000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-470000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-355000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-406000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-441000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-367000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-242000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-289000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-273000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3859000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3373000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3175000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2860000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2550000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2491000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2428000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2711000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2162000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1886000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2634000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3638000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3958000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2773000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2670000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2815000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3044000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2973000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2980000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3009000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2863000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2878000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2206000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3044000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2822000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3549000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3803000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-8778000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2424000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2515000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2348000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3859000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3373000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3175000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2860000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2550000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2491000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2428000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2711000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2162000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1886000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2634000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3638000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3958000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2773000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2670000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2815000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3044000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2973000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2980000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3009000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2863000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2878000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2206000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3044000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2822000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3549000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3803000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-8778000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2424000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2515000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2348000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E38" s="2">
         <v>46137</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44219</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44128</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44037</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43946</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43764</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43673</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43582</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43491</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43400</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43218</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43127</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,1106 +4280,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7218000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7083000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7458000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8400000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8346000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8161000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8556000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9065000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7508000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8913000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13715000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9602000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10123000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8044000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9009000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7292000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7079000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6952000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6731000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7619000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9175000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7356000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11800000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10825000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11809000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10367000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8475000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8587000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11750000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10251000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9835000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8410000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8934000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6719000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>17624000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>11043000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>11708000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8116000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>10898000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>8583000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8700000</v>
+      </c>
+      <c r="E42" s="3">
         <v>9557000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8319000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7336000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8327000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8231000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9088000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10358000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11096000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10607000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12519000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14296000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16211000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15244000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13052000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12492000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12188000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13156000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14382000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>15727000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>15343000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>16229000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>18795000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19190000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17610000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>18208000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>18587000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>19448000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>21663000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>24392000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>30548000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>34183000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>37614000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>47712000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>56059000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>60545000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>58784000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>59858000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>60947000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>62385000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12762000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11216000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11350000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9712000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11462000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8235000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8743000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7580000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11423000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8570000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8360000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8247000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9206000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8506000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10194000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10422000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11827000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10887000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11400000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10776000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11546000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10373000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10534000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10285000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11723000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10372000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>9157000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9904000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10586000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8824000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8802000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10503000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9142000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8888000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9244000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10002000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9274000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8954000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9346000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5694000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4708000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3920000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3395000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3164000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2832000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2927000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3143000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3373000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3118000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3209000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3342000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3644000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3474000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3140000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2664000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2568000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2231000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2059000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1832000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1559000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1579000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1436000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1303000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1282000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1212000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1353000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1344000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1383000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1513000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1701000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1572000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1846000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1900000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1896000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1693000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1616000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1366000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1264000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1176000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4282000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3995000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4083000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4032000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3123000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4602000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4606000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4843000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2697000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3913000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3759000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3794000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3973000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4680000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3120000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3271000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3055000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2755000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2227000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1634000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1489000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1523000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1346000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1386000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1149000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1148000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2433000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2373000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2331000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2231000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2134000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2940000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1668000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1583000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1555000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1593000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1348000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1329000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1651000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38665000</v>
+      </c>
+      <c r="E46" s="3">
         <v>36559000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35131000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32876000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34986000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32816000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34681000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35752000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36862000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35886000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42127000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39659000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43348000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39950000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38515000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36141000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36717000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>35981000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36799000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37588000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>39112000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37060000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>43911000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>42989000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>43573000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>41307000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>40053000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>41716000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47755000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47311000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>53117000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>55686000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>61837000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>67141000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>86050000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>84080000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>83703000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>79962000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>83392000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>83141000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3299000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2900000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2100000</v>
       </c>
       <c r="F47" s="3">
         <v>2100000</v>
       </c>
       <c r="G47" s="3">
-        <v>1900000</v>
+        <v>2100000</v>
       </c>
       <c r="H47" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="I47" s="3">
         <v>2000000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2088000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2175000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2363000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2350000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2538000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2925000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3113000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3300000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3554000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3618000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4009000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3959000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4024000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4546000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4884000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5068000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5100000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5516000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6992000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6024000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5973000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6048000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6158000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6112000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5813000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5884000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5978000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5884000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5895000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5823000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5721000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5518000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5671000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>5775000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4155000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4027000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3759000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3551000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3414000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3295000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3126000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3174000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3156000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3008000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2983000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3001000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3056000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3064000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2942000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2901000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3000000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3070000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3218000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3356000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3433000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3295000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3360000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3365000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3374000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3465000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3621000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3769000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2789000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2834000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2931000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2956000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3006000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3082000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3113000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3202000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3322000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3395000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3422000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3499000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67034000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67142000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>67541000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>67832000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>68311000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>68667000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>68858000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69518000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>69879000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>70452000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>40765000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>40814000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>40353000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>40335000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>40522000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>40520000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>40873000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>41263000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>41758000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>42152000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>41787000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>41406000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>36195000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>36116000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>35382000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>35197000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>35518000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>35685000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>35730000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>35942000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>35563000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>36102000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34258000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34335000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>32865000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>32910000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>32305000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>32220000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>28939000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>29120000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2866000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2218000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2143000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2110000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1358000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2741000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2791000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2789000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1215000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2524000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2059000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1957000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1923000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1670000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10307000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9874000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9403000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8524000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8463000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8339000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8281000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7067000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7035000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7017000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5532000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5401000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5261000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5274000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5361000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5088000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5038000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4801000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3705000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3566000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3587000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4507000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4767000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4855000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4824000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>4752000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>129637000</v>
+      </c>
+      <c r="E54" s="3">
         <v>125546000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123371000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>121102000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122291000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119782000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>121375000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123333000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>124413000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122998000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>101174000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>98782000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>101852000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97529000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>95840000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>93054000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>94002000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>92797000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>94262000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>95981000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>97497000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93896000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95601000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95003000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>94853000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>91394000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>90426000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>92492000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97793000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>97287000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>102462000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>105429000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>108784000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>114008000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>131510000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>130522000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>129818000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>125950000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>126248000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>126287000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,740 +6120,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3660000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3179000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2947000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2603000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2734000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2506000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2285000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2435000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2802000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2604000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2386000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2594000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2842000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2967000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2329000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2316000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2281000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2289000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2101000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2261000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2362000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2440000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1867000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2294000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2218000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2393000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1935000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2016000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2059000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2022000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1655000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1805000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1904000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1552000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1060000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1155000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1385000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1219000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>957000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>996000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10565000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12342000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9124000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7128000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5607000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6774000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11782000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12729000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11716000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12235000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5269000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1302000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2063000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2070000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1250000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1249000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1099000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1000000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2502000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>506000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2508000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2000000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5000000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5002000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3005000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4506000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1499000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4000000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>10191000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7777000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9737000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7241000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5238000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7736000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>13741000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>10239000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7992000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4248000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4451000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>4155000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23243000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20730000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21221000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22656000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23112000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22005000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22653000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22517000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22458000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22058000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19980000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20100000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22420000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20330000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23673000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21331000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22260000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20861000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21312000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20471000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21387000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19822000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20401000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19695000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>20108000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19038000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18654000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18581000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19462000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18114000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18087000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17368000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>19893000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>19354000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>20563000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>17890000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>18206000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>17251000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>17300000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>18066000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41525000</v>
+      </c>
+      <c r="E60" s="3">
         <v>39541000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36786000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35451000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35064000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34495000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40019000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40542000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40584000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40108000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30851000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27035000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31309000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28719000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27252000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24896000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25640000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24150000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25915000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23238000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26257000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24262000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27268000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>26991000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25331000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25937000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22088000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>24597000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31712000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>27913000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29479000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>26414000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27035000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>28642000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>35364000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>29284000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>27583000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>22718000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>22708000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>23217000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20620000</v>
+      </c>
+      <c r="E61" s="3">
         <v>20659000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22616000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22509000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24036000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23971000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20640000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20561000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20527000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20979000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7387000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7423000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7389000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7423000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7637000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7629000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8416000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8418000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8969000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8996000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9018000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9532000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9554000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9564000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>11578000</v>
       </c>
       <c r="AB61" s="3">
         <v>11578000</v>
       </c>
       <c r="AC61" s="3">
+        <v>11578000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>14494000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14497000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14475000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>15921000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15893000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18323000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20331000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>20336000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>25625000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>25684000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>25725000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>28222000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>30471000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>30634000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4329000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4332000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4042000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4101000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3910000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3471000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3390000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5066000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5543000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4419000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4925000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7267000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7097000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8081000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19477000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20257000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20173000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>19829000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19882000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21046000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20947000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19897000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19658000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20291000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20024000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18171000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18311000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18975000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>18035000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16649000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16301000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16844000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18214000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18369000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>18539000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>10004000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>10373000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9628000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9251000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>9023000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79352000</v>
+      </c>
+      <c r="E66" s="3">
         <v>76685000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75648000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74229000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>75448000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>73847000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75845000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78056000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78956000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77230000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54923000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53572000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57499000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55234000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54366000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52782000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>54229000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>52397000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54766000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>53280000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56222000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>53691000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>56480000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>56846000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>56933000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>55686000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54893000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>58069000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64222000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60483000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>61673000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>61581000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>65580000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>67347000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>79528000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>64972000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>63681000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>60568000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>62437000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>62881000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7621,8 +7788,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1565000</v>
+      </c>
+      <c r="E72" s="3">
         <v>704000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-364000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>152000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>502000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>662000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1087000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2055000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2761000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2689000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1639000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>262000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-364000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-594000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1319000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-724000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2006000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>553000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-654000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1456000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2351000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2756000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3874000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4384000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5083000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5903000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2877000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>538000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3169000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1233000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3709000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7364000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>20647000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>20838000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>20721000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>20027000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>19694000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50285000</v>
+      </c>
+      <c r="E76" s="3">
         <v>48861000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47723000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46873000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46843000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45935000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45530000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45277000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45457000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45768000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46251000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45210000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44353000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42295000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41474000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>40272000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>39773000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40400000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>39496000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>42701000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>41275000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40205000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39121000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>38157000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>37920000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35708000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>35533000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>34423000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33571000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36804000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>40789000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>43848000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>43204000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>46661000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>51982000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>65550000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>66137000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>65382000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>63811000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>63406000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E80" s="2">
         <v>46137</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44219</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44128</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44037</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43946</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43764</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43673</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43582</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43491</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43400</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43218</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43127</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3859000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3373000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3175000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2860000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2550000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2491000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2428000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2711000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2162000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1886000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2634000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3638000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3958000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2773000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2670000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2815000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3044000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2973000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2980000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3009000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2863000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2878000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2206000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3044000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2822000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3549000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3803000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-8778000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2424000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2515000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2348000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,130 +8965,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E83" s="3">
         <v>113000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>156000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>199000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>66000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>310000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>176000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>148000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>84000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>221000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>209000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>186000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>111000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>206000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>438000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>415000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>430000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>478000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>516000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>533000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>489000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>486000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>436000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>451000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>444000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>446000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>457000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>461000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>464000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>481000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>487000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>465000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>516000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>564000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>546000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>566000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>578000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>560000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>549000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5386000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3757000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1822000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3212000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4234000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4057000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2241000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3661000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3730000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3971000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>808000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2371000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5966000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5219000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4739000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3962000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3677000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3661000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2461000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3427000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4504000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3880000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2974000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4096000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3802000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4237000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3800000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3587000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3942000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4329000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3797000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3763000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4100000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2416000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4070000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3080000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>4001000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3373000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3772000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2730000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,130 +9885,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-390000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-414000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-283000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-323000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-217000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-261000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-210000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-217000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-198000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-168000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-170000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-134000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-233000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-270000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-170000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-176000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-139000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-106000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-110000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-122000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-162000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-172000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-187000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-208000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-189000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-208000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-228000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-261000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-214000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-241000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-211000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-168000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-208000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-230000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-251000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-264000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2070000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1306000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>156000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-273000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>505000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1022000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>479000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-828000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22815000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2213000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>952000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1220000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2594000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-494000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-799000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>869000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>653000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1051000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1020000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>348000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3105000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>182000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2710000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>499000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>236000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>843000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1922000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2689000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5606000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>3867000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2675000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>8069000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5760000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>3990000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2495000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>695000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1710000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>418000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-5396000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,130 +10430,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1660000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>1617000</v>
       </c>
       <c r="F96" s="3">
         <v>1617000</v>
       </c>
       <c r="G96" s="3">
+        <v>1617000</v>
+      </c>
+      <c r="H96" s="3">
         <v>1625000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1627000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1593000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1592000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1606000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1615000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1583000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1580000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1589000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1593000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-1560000</v>
       </c>
       <c r="R96" s="3">
         <v>-1560000</v>
       </c>
       <c r="S96" s="3">
+        <v>-1560000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1567000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1555000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1541000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1561000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1562000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1560000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1521000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1520000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1525000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1519000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-1486000</v>
       </c>
       <c r="AD96" s="3">
         <v>-1486000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1486000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1519000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1470000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1500000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1535000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1572000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1425000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1448000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1451000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1304000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1308000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,183 +10928,189 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5006000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2039000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3949000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5137000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3945000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2784000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4507000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14072000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1079000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3800000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2650000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3495000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2626000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2855000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3618000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3975000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4399000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3970000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2269000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5219000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2178000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2859000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2602000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4757000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8668000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5132000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9541000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6271000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6945000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-9954000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19081000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1479000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4445000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1875000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>3618000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>13000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-45000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-15000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-93000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>98000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-95000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-58000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>98000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-95000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-58000</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>24</v>
@@ -10873,8 +11121,8 @@
       <c r="W101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -10930,126 +11178,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-376000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-942000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-509000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-590000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1366000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1597000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4779000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4113000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-522000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2081000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-963000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1717000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>213000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>870000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>217000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-887000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1563000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2583000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4444000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>978000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-987000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1442000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1871000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3159000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1499000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>394000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1393000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-507000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2215000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10905000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>6581000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-665000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>3592000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2782000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2315000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>952000</v>
       </c>
     </row>
